--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ103"/>
+  <dimension ref="A1:AZ107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128721654</v>
+        <v>137406599</v>
       </c>
       <c r="B2" t="n">
-        <v>87309</v>
+        <v>101655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3674</v>
+        <v>1333</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Gotlandssippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Pulsatilla vulgaris subsp. gotlandica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Johanss.) Zämelis &amp; Paegle</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gyle, Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>716862</v>
+        <v>716908</v>
       </c>
       <c r="R2" t="n">
-        <v>6367895</v>
+        <v>6367937</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,47 +745,58 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128721654</t>
+          <t>https://artportalen.se/Sighting/137406599</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133905919</v>
+        <v>128721654</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>87309</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +804,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Gyle, Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>716736</v>
+        <v>716862</v>
       </c>
       <c r="R3" t="n">
-        <v>6367574</v>
+        <v>6367895</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,17 +858,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök vid basen av död gran.</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,27 +878,27 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133905919</t>
+          <t>https://artportalen.se/Sighting/128721654</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133905920</v>
+        <v>137406590</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>87541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,42 +906,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>3674</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>716715</v>
+        <v>716710</v>
       </c>
       <c r="R4" t="n">
-        <v>6367553</v>
+        <v>6367629</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,12 +960,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -984,65 +990,70 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133905920</t>
+          <t>https://artportalen.se/Sighting/137406590</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134649762</v>
+        <v>133905919</v>
       </c>
       <c r="B5" t="n">
-        <v>43472</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ala Ollajvs nedre, Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>716839</v>
+        <v>716736</v>
       </c>
       <c r="R5" t="n">
-        <v>6367941</v>
+        <v>6367574</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,27 +1077,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>Födosök vid basen av död gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,65 +1102,70 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649762</t>
+          <t>https://artportalen.se/Sighting/133905919</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134649764</v>
+        <v>133905920</v>
       </c>
       <c r="B6" t="n">
-        <v>43472</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101242</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala Ollajvs nedre, Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>716837</v>
+        <v>716715</v>
       </c>
       <c r="R6" t="n">
-        <v>6367924</v>
+        <v>6367553</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1183,22 +1189,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,24 +1209,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649764</t>
+          <t>https://artportalen.se/Sighting/133905920</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134649768</v>
+        <v>134649762</v>
       </c>
       <c r="B7" t="n">
         <v>43472</v>
@@ -1265,13 +1261,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>716824</v>
+        <v>716839</v>
       </c>
       <c r="R7" t="n">
-        <v>6367834</v>
+        <v>6367941</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1300,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1306,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,13 +1337,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649768</t>
+          <t>https://artportalen.se/Sighting/134649762</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134649770</v>
+        <v>134649764</v>
       </c>
       <c r="B8" t="n">
         <v>43472</v>
@@ -1377,13 +1378,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>716808</v>
+        <v>716837</v>
       </c>
       <c r="R8" t="n">
-        <v>6367826</v>
+        <v>6367924</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1412,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1453,13 +1449,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649770</t>
+          <t>https://artportalen.se/Sighting/134649764</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134649774</v>
+        <v>134649768</v>
       </c>
       <c r="B9" t="n">
         <v>43472</v>
@@ -1494,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>716794</v>
+        <v>716824</v>
       </c>
       <c r="R9" t="n">
-        <v>6367798</v>
+        <v>6367834</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,7 +1525,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1539,12 +1535,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1570,13 +1561,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649774</t>
+          <t>https://artportalen.se/Sighting/134649768</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134649775</v>
+        <v>134649770</v>
       </c>
       <c r="B10" t="n">
         <v>43472</v>
@@ -1611,13 +1602,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>716785</v>
+        <v>716808</v>
       </c>
       <c r="R10" t="n">
-        <v>6367787</v>
+        <v>6367826</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1646,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1687,13 +1678,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649775</t>
+          <t>https://artportalen.se/Sighting/134649770</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134649779</v>
+        <v>134649774</v>
       </c>
       <c r="B11" t="n">
         <v>43472</v>
@@ -1728,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>716779</v>
+        <v>716794</v>
       </c>
       <c r="R11" t="n">
-        <v>6367766</v>
+        <v>6367798</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1763,7 +1754,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1764,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1804,13 +1795,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649779</t>
+          <t>https://artportalen.se/Sighting/134649774</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134649781</v>
+        <v>134649775</v>
       </c>
       <c r="B12" t="n">
         <v>43472</v>
@@ -1845,13 +1836,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>716772</v>
+        <v>716785</v>
       </c>
       <c r="R12" t="n">
-        <v>6367771</v>
+        <v>6367787</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,7 +1871,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,12 +1881,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,13 +1912,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649781</t>
+          <t>https://artportalen.se/Sighting/134649775</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134649783</v>
+        <v>134649779</v>
       </c>
       <c r="B13" t="n">
         <v>43472</v>
@@ -1962,13 +1953,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>716771</v>
+        <v>716779</v>
       </c>
       <c r="R13" t="n">
-        <v>6367772</v>
+        <v>6367766</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1997,7 +1988,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +1998,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2033,13 +2029,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649783</t>
+          <t>https://artportalen.se/Sighting/134649779</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134649786</v>
+        <v>134649781</v>
       </c>
       <c r="B14" t="n">
         <v>43472</v>
@@ -2074,13 +2070,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>716743</v>
+        <v>716772</v>
       </c>
       <c r="R14" t="n">
-        <v>6367747</v>
+        <v>6367771</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2109,7 +2105,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2115,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2145,13 +2146,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649786</t>
+          <t>https://artportalen.se/Sighting/134649781</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134649788</v>
+        <v>134649783</v>
       </c>
       <c r="B15" t="n">
         <v>43472</v>
@@ -2186,10 +2187,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>716722</v>
+        <v>716771</v>
       </c>
       <c r="R15" t="n">
-        <v>6367778</v>
+        <v>6367772</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2221,7 +2222,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2232,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,13 +2258,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649788</t>
+          <t>https://artportalen.se/Sighting/134649783</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134649791</v>
+        <v>134649786</v>
       </c>
       <c r="B16" t="n">
         <v>43472</v>
@@ -2298,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>716703</v>
+        <v>716743</v>
       </c>
       <c r="R16" t="n">
-        <v>6367737</v>
+        <v>6367747</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2333,7 +2334,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,12 +2344,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:25</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,13 +2370,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649791</t>
+          <t>https://artportalen.se/Sighting/134649786</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134649793</v>
+        <v>134649788</v>
       </c>
       <c r="B17" t="n">
         <v>43472</v>
@@ -2415,10 +2411,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>716689</v>
+        <v>716722</v>
       </c>
       <c r="R17" t="n">
-        <v>6367735</v>
+        <v>6367778</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2450,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2486,13 +2482,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649793</t>
+          <t>https://artportalen.se/Sighting/134649788</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134649797</v>
+        <v>134649791</v>
       </c>
       <c r="B18" t="n">
         <v>43472</v>
@@ -2527,13 +2523,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>716677</v>
+        <v>716703</v>
       </c>
       <c r="R18" t="n">
-        <v>6367701</v>
+        <v>6367737</v>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2562,7 +2558,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2568,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,13 +2599,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649797</t>
+          <t>https://artportalen.se/Sighting/134649791</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134649799</v>
+        <v>134649793</v>
       </c>
       <c r="B19" t="n">
         <v>43472</v>
@@ -2639,13 +2640,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>716669</v>
+        <v>716689</v>
       </c>
       <c r="R19" t="n">
-        <v>6367709</v>
+        <v>6367735</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2674,7 +2675,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,12 +2685,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>10-tal</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,13 +2711,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649799</t>
+          <t>https://artportalen.se/Sighting/134649793</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134649803</v>
+        <v>134649797</v>
       </c>
       <c r="B20" t="n">
         <v>43472</v>
@@ -2756,13 +2752,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>716693</v>
+        <v>716677</v>
       </c>
       <c r="R20" t="n">
-        <v>6367674</v>
+        <v>6367701</v>
       </c>
       <c r="S20" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2791,7 +2787,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,12 +2797,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,13 +2823,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649803</t>
+          <t>https://artportalen.se/Sighting/134649797</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134649805</v>
+        <v>134649799</v>
       </c>
       <c r="B21" t="n">
         <v>43472</v>
@@ -2873,13 +2864,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>716711</v>
+        <v>716669</v>
       </c>
       <c r="R21" t="n">
-        <v>6367631</v>
+        <v>6367709</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2899,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,12 +2909,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>3 st</t>
+          <t>10-tal</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,13 +2940,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649805</t>
+          <t>https://artportalen.se/Sighting/134649799</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134649809</v>
+        <v>134649803</v>
       </c>
       <c r="B22" t="n">
         <v>43472</v>
@@ -2990,13 +2981,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>716711</v>
+        <v>716693</v>
       </c>
       <c r="R22" t="n">
-        <v>6367623</v>
+        <v>6367674</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3025,7 +3016,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3035,7 +3026,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3066,13 +3057,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649809</t>
+          <t>https://artportalen.se/Sighting/134649803</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134649811</v>
+        <v>134649805</v>
       </c>
       <c r="B23" t="n">
         <v>43472</v>
@@ -3107,10 +3098,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>716705</v>
+        <v>716711</v>
       </c>
       <c r="R23" t="n">
-        <v>6367588</v>
+        <v>6367631</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3142,7 +3133,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3152,12 +3143,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>5 st</t>
+          <t>3 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3183,13 +3174,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649811</t>
+          <t>https://artportalen.se/Sighting/134649805</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134649813</v>
+        <v>134649809</v>
       </c>
       <c r="B24" t="n">
         <v>43472</v>
@@ -3224,10 +3215,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>716653</v>
+        <v>716711</v>
       </c>
       <c r="R24" t="n">
-        <v>6367562</v>
+        <v>6367623</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3259,7 +3250,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3269,12 +3260,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4 st</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3300,13 +3291,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649813</t>
+          <t>https://artportalen.se/Sighting/134649809</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134649816</v>
+        <v>134649811</v>
       </c>
       <c r="B25" t="n">
         <v>43472</v>
@@ -3341,13 +3332,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>716640</v>
+        <v>716705</v>
       </c>
       <c r="R25" t="n">
-        <v>6367572</v>
+        <v>6367588</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3376,7 +3367,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3386,7 +3377,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>5 st</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,13 +3408,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649816</t>
+          <t>https://artportalen.se/Sighting/134649811</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134649818</v>
+        <v>134649813</v>
       </c>
       <c r="B26" t="n">
         <v>43472</v>
@@ -3453,13 +3449,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>716621</v>
+        <v>716653</v>
       </c>
       <c r="R26" t="n">
-        <v>6367585</v>
+        <v>6367562</v>
       </c>
       <c r="S26" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3488,7 +3484,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3498,7 +3494,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3524,13 +3525,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649818</t>
+          <t>https://artportalen.se/Sighting/134649813</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134649820</v>
+        <v>134649816</v>
       </c>
       <c r="B27" t="n">
         <v>43472</v>
@@ -3565,13 +3566,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>716623</v>
+        <v>716640</v>
       </c>
       <c r="R27" t="n">
-        <v>6367544</v>
+        <v>6367572</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3600,7 +3601,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3610,12 +3611,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>2 st</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3641,13 +3637,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649820</t>
+          <t>https://artportalen.se/Sighting/134649816</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134649822</v>
+        <v>134649818</v>
       </c>
       <c r="B28" t="n">
         <v>43472</v>
@@ -3682,13 +3678,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>716633</v>
+        <v>716621</v>
       </c>
       <c r="R28" t="n">
-        <v>6367540</v>
+        <v>6367585</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3717,7 +3713,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3727,7 +3723,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3753,13 +3749,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649822</t>
+          <t>https://artportalen.se/Sighting/134649818</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134649826</v>
+        <v>134649820</v>
       </c>
       <c r="B29" t="n">
         <v>43472</v>
@@ -3794,10 +3790,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>716657</v>
+        <v>716623</v>
       </c>
       <c r="R29" t="n">
-        <v>6367550</v>
+        <v>6367544</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3829,7 +3825,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3839,12 +3835,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>3 st kring stående död ved</t>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3870,13 +3866,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649826</t>
+          <t>https://artportalen.se/Sighting/134649820</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134658143</v>
+        <v>134649822</v>
       </c>
       <c r="B30" t="n">
         <v>43472</v>
@@ -3907,14 +3903,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ala, Gtl</t>
+          <t>Ala Ollajvs nedre, Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>716852</v>
+        <v>716633</v>
       </c>
       <c r="R30" t="n">
-        <v>6367927</v>
+        <v>6367540</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3946,7 +3942,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3956,12 +3952,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1st</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3976,24 +3967,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658143</t>
+          <t>https://artportalen.se/Sighting/134649822</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134658147</v>
+        <v>134649826</v>
       </c>
       <c r="B31" t="n">
         <v>43472</v>
@@ -4024,14 +4015,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ala, Gtl</t>
+          <t>Ala Ollajvs nedre, Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>716840</v>
+        <v>716657</v>
       </c>
       <c r="R31" t="n">
-        <v>6367947</v>
+        <v>6367550</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4063,7 +4054,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4073,12 +4064,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>3 st kring stående död ved</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4093,24 +4084,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Esmeralda  Svanberg</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658147</t>
+          <t>https://artportalen.se/Sighting/134649826</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134658148</v>
+        <v>134658143</v>
       </c>
       <c r="B32" t="n">
         <v>43472</v>
@@ -4145,10 +4136,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>716828</v>
+        <v>716852</v>
       </c>
       <c r="R32" t="n">
-        <v>6367945</v>
+        <v>6367927</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4180,7 +4171,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4190,7 +4181,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
@@ -4221,13 +4212,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658148</t>
+          <t>https://artportalen.se/Sighting/134658143</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134658149</v>
+        <v>134658147</v>
       </c>
       <c r="B33" t="n">
         <v>43472</v>
@@ -4262,10 +4253,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>716830</v>
+        <v>716840</v>
       </c>
       <c r="R33" t="n">
-        <v>6367953</v>
+        <v>6367947</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4297,7 +4288,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4307,12 +4298,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:48</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4338,13 +4329,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658149</t>
+          <t>https://artportalen.se/Sighting/134658147</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134658150</v>
+        <v>134658148</v>
       </c>
       <c r="B34" t="n">
         <v>43472</v>
@@ -4379,13 +4370,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>716853</v>
+        <v>716828</v>
       </c>
       <c r="R34" t="n">
-        <v>6367848</v>
+        <v>6367945</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4414,7 +4405,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4424,7 +4415,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4455,13 +4446,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658150</t>
+          <t>https://artportalen.se/Sighting/134658148</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134658154</v>
+        <v>134658149</v>
       </c>
       <c r="B35" t="n">
         <v>43472</v>
@@ -4496,10 +4487,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>716836</v>
+        <v>716830</v>
       </c>
       <c r="R35" t="n">
-        <v>6367837</v>
+        <v>6367953</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4531,7 +4522,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4541,7 +4532,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -4572,13 +4563,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658154</t>
+          <t>https://artportalen.se/Sighting/134658149</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134658155</v>
+        <v>134658150</v>
       </c>
       <c r="B36" t="n">
         <v>43472</v>
@@ -4613,13 +4604,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>716848</v>
+        <v>716853</v>
       </c>
       <c r="R36" t="n">
-        <v>6367828</v>
+        <v>6367848</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4648,7 +4639,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4658,7 +4649,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
@@ -4689,13 +4680,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658155</t>
+          <t>https://artportalen.se/Sighting/134658150</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134658157</v>
+        <v>134658154</v>
       </c>
       <c r="B37" t="n">
         <v>43472</v>
@@ -4730,13 +4721,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>716816</v>
+        <v>716836</v>
       </c>
       <c r="R37" t="n">
-        <v>6367819</v>
+        <v>6367837</v>
       </c>
       <c r="S37" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4765,7 +4756,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4775,7 +4766,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
@@ -4806,13 +4797,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658157</t>
+          <t>https://artportalen.se/Sighting/134658154</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134658158</v>
+        <v>134658155</v>
       </c>
       <c r="B38" t="n">
         <v>43472</v>
@@ -4847,10 +4838,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>716812</v>
+        <v>716848</v>
       </c>
       <c r="R38" t="n">
-        <v>6367809</v>
+        <v>6367828</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4882,7 +4873,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4892,12 +4883,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>3st</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4923,13 +4914,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658158</t>
+          <t>https://artportalen.se/Sighting/134658155</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134658160</v>
+        <v>134658157</v>
       </c>
       <c r="B39" t="n">
         <v>43472</v>
@@ -4967,10 +4958,10 @@
         <v>716816</v>
       </c>
       <c r="R39" t="n">
-        <v>6367798</v>
+        <v>6367819</v>
       </c>
       <c r="S39" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4999,7 +4990,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5009,12 +5000,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5040,13 +5031,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658160</t>
+          <t>https://artportalen.se/Sighting/134658157</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134658163</v>
+        <v>134658158</v>
       </c>
       <c r="B40" t="n">
         <v>43472</v>
@@ -5081,13 +5072,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>716801</v>
+        <v>716812</v>
       </c>
       <c r="R40" t="n">
-        <v>6367795</v>
+        <v>6367809</v>
       </c>
       <c r="S40" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5116,7 +5107,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5126,12 +5117,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5157,13 +5148,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658163</t>
+          <t>https://artportalen.se/Sighting/134658158</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134658165</v>
+        <v>134658160</v>
       </c>
       <c r="B41" t="n">
         <v>43472</v>
@@ -5198,13 +5189,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>716786</v>
+        <v>716816</v>
       </c>
       <c r="R41" t="n">
-        <v>6367782</v>
+        <v>6367798</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5233,7 +5224,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5243,12 +5234,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5274,13 +5265,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658165</t>
+          <t>https://artportalen.se/Sighting/134658160</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134658168</v>
+        <v>134658163</v>
       </c>
       <c r="B42" t="n">
         <v>43472</v>
@@ -5315,13 +5306,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>716758</v>
+        <v>716801</v>
       </c>
       <c r="R42" t="n">
-        <v>6367760</v>
+        <v>6367795</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5350,7 +5341,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5360,7 +5351,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
@@ -5391,13 +5382,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658168</t>
+          <t>https://artportalen.se/Sighting/134658163</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134658169</v>
+        <v>134658165</v>
       </c>
       <c r="B43" t="n">
         <v>43472</v>
@@ -5432,13 +5423,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>716741</v>
+        <v>716786</v>
       </c>
       <c r="R43" t="n">
-        <v>6367746</v>
+        <v>6367782</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5467,7 +5458,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5477,12 +5468,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5508,13 +5499,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658169</t>
+          <t>https://artportalen.se/Sighting/134658165</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134658171</v>
+        <v>134658168</v>
       </c>
       <c r="B44" t="n">
         <v>43472</v>
@@ -5549,10 +5540,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>716745</v>
+        <v>716758</v>
       </c>
       <c r="R44" t="n">
-        <v>6367735</v>
+        <v>6367760</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5584,7 +5575,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5594,7 +5585,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:17</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
@@ -5625,13 +5616,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658171</t>
+          <t>https://artportalen.se/Sighting/134658168</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134658175</v>
+        <v>134658169</v>
       </c>
       <c r="B45" t="n">
         <v>43472</v>
@@ -5666,13 +5657,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>716731</v>
+        <v>716741</v>
       </c>
       <c r="R45" t="n">
-        <v>6367729</v>
+        <v>6367746</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5701,7 +5692,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5711,12 +5702,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:24</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5742,13 +5733,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658175</t>
+          <t>https://artportalen.se/Sighting/134658169</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134658176</v>
+        <v>134658171</v>
       </c>
       <c r="B46" t="n">
         <v>43472</v>
@@ -5783,13 +5774,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>716721</v>
+        <v>716745</v>
       </c>
       <c r="R46" t="n">
-        <v>6367714</v>
+        <v>6367735</v>
       </c>
       <c r="S46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5818,7 +5809,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5828,12 +5819,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:25</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>4st individer i typisk förökningsyta</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5859,13 +5850,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658176</t>
+          <t>https://artportalen.se/Sighting/134658171</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134658179</v>
+        <v>134658175</v>
       </c>
       <c r="B47" t="n">
         <v>43472</v>
@@ -5903,7 +5894,7 @@
         <v>716731</v>
       </c>
       <c r="R47" t="n">
-        <v>6367709</v>
+        <v>6367729</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5935,7 +5926,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5945,12 +5936,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:27</t>
+          <t>10:24</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5976,13 +5967,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658179</t>
+          <t>https://artportalen.se/Sighting/134658175</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134658180</v>
+        <v>134658176</v>
       </c>
       <c r="B48" t="n">
         <v>43472</v>
@@ -6017,13 +6008,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>716711</v>
+        <v>716721</v>
       </c>
       <c r="R48" t="n">
-        <v>6367725</v>
+        <v>6367714</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6052,7 +6043,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6062,12 +6053,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4st individer i typisk förökningsyta</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6093,13 +6084,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658180</t>
+          <t>https://artportalen.se/Sighting/134658176</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134658181</v>
+        <v>134658179</v>
       </c>
       <c r="B49" t="n">
         <v>43472</v>
@@ -6134,10 +6125,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>716699</v>
+        <v>716731</v>
       </c>
       <c r="R49" t="n">
-        <v>6367717</v>
+        <v>6367709</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6169,7 +6160,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6179,12 +6170,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:27</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6210,13 +6201,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658181</t>
+          <t>https://artportalen.se/Sighting/134658179</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134658183</v>
+        <v>134658180</v>
       </c>
       <c r="B50" t="n">
         <v>43472</v>
@@ -6251,13 +6242,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>716688</v>
+        <v>716711</v>
       </c>
       <c r="R50" t="n">
-        <v>6367710</v>
+        <v>6367725</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6286,7 +6277,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6296,7 +6287,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
@@ -6327,13 +6318,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658183</t>
+          <t>https://artportalen.se/Sighting/134658180</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134658184</v>
+        <v>134658181</v>
       </c>
       <c r="B51" t="n">
         <v>43472</v>
@@ -6368,10 +6359,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>716697</v>
+        <v>716699</v>
       </c>
       <c r="R51" t="n">
-        <v>6367699</v>
+        <v>6367717</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6403,7 +6394,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6413,12 +6404,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>1st</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6444,13 +6435,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658184</t>
+          <t>https://artportalen.se/Sighting/134658181</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134658185</v>
+        <v>134658183</v>
       </c>
       <c r="B52" t="n">
         <v>43472</v>
@@ -6485,10 +6476,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>716708</v>
+        <v>716688</v>
       </c>
       <c r="R52" t="n">
-        <v>6367696</v>
+        <v>6367710</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6520,7 +6511,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6530,7 +6521,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -6561,13 +6552,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658185</t>
+          <t>https://artportalen.se/Sighting/134658183</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134658186</v>
+        <v>134658184</v>
       </c>
       <c r="B53" t="n">
         <v>43472</v>
@@ -6602,10 +6593,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>716706</v>
+        <v>716697</v>
       </c>
       <c r="R53" t="n">
-        <v>6367681</v>
+        <v>6367699</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6637,7 +6628,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6647,7 +6638,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
@@ -6678,13 +6669,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658186</t>
+          <t>https://artportalen.se/Sighting/134658184</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134658187</v>
+        <v>134658185</v>
       </c>
       <c r="B54" t="n">
         <v>43472</v>
@@ -6719,10 +6710,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>716730</v>
+        <v>716708</v>
       </c>
       <c r="R54" t="n">
-        <v>6367659</v>
+        <v>6367696</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6754,7 +6745,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6764,7 +6755,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -6795,13 +6786,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658187</t>
+          <t>https://artportalen.se/Sighting/134658185</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134658189</v>
+        <v>134658186</v>
       </c>
       <c r="B55" t="n">
         <v>43472</v>
@@ -6836,10 +6827,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>716733</v>
+        <v>716706</v>
       </c>
       <c r="R55" t="n">
-        <v>6367643</v>
+        <v>6367681</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6871,7 +6862,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6881,12 +6872,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6912,13 +6903,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658189</t>
+          <t>https://artportalen.se/Sighting/134658186</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134658190</v>
+        <v>134658187</v>
       </c>
       <c r="B56" t="n">
         <v>43472</v>
@@ -6953,10 +6944,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>716740</v>
+        <v>716730</v>
       </c>
       <c r="R56" t="n">
-        <v>6367639</v>
+        <v>6367659</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6988,7 +6979,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6998,12 +6989,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>3st individer</t>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7029,13 +7020,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658190</t>
+          <t>https://artportalen.se/Sighting/134658187</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134658191</v>
+        <v>134658189</v>
       </c>
       <c r="B57" t="n">
         <v>43472</v>
@@ -7070,13 +7061,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>716732</v>
+        <v>716733</v>
       </c>
       <c r="R57" t="n">
-        <v>6367628</v>
+        <v>6367643</v>
       </c>
       <c r="S57" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7105,7 +7096,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -7115,12 +7106,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>3st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7146,13 +7137,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658191</t>
+          <t>https://artportalen.se/Sighting/134658189</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134658192</v>
+        <v>134658190</v>
       </c>
       <c r="B58" t="n">
         <v>43472</v>
@@ -7187,10 +7178,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>716750</v>
+        <v>716740</v>
       </c>
       <c r="R58" t="n">
-        <v>6367630</v>
+        <v>6367639</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7222,7 +7213,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7232,12 +7223,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>3st</t>
+          <t>3st individer</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7263,13 +7254,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658192</t>
+          <t>https://artportalen.se/Sighting/134658190</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134658193</v>
+        <v>134658191</v>
       </c>
       <c r="B59" t="n">
         <v>43472</v>
@@ -7304,13 +7295,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>716745</v>
+        <v>716732</v>
       </c>
       <c r="R59" t="n">
-        <v>6367605</v>
+        <v>6367628</v>
       </c>
       <c r="S59" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7339,7 +7330,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7349,12 +7340,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7380,13 +7371,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658193</t>
+          <t>https://artportalen.se/Sighting/134658191</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134658195</v>
+        <v>134658192</v>
       </c>
       <c r="B60" t="n">
         <v>43472</v>
@@ -7421,10 +7412,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>716754</v>
+        <v>716750</v>
       </c>
       <c r="R60" t="n">
-        <v>6367591</v>
+        <v>6367630</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7456,7 +7447,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7466,12 +7457,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7497,13 +7488,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658195</t>
+          <t>https://artportalen.se/Sighting/134658192</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134658196</v>
+        <v>134658193</v>
       </c>
       <c r="B61" t="n">
         <v>43472</v>
@@ -7538,13 +7529,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>716748</v>
+        <v>716745</v>
       </c>
       <c r="R61" t="n">
-        <v>6367576</v>
+        <v>6367605</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7573,7 +7564,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7583,7 +7574,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr">
@@ -7614,13 +7605,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658196</t>
+          <t>https://artportalen.se/Sighting/134658193</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134658198</v>
+        <v>134658195</v>
       </c>
       <c r="B62" t="n">
         <v>43472</v>
@@ -7655,13 +7646,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>716741</v>
+        <v>716754</v>
       </c>
       <c r="R62" t="n">
-        <v>6367556</v>
+        <v>6367591</v>
       </c>
       <c r="S62" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7690,7 +7681,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7700,12 +7691,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:07</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>3st</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7731,13 +7722,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658198</t>
+          <t>https://artportalen.se/Sighting/134658195</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134658199</v>
+        <v>134658196</v>
       </c>
       <c r="B63" t="n">
         <v>43472</v>
@@ -7772,10 +7763,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>716721</v>
+        <v>716748</v>
       </c>
       <c r="R63" t="n">
-        <v>6367546</v>
+        <v>6367576</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7807,7 +7798,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7817,12 +7808,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>4st</t>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7848,13 +7839,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658199</t>
+          <t>https://artportalen.se/Sighting/134658196</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134658200</v>
+        <v>134658198</v>
       </c>
       <c r="B64" t="n">
         <v>43472</v>
@@ -7889,13 +7880,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>716726</v>
+        <v>716741</v>
       </c>
       <c r="R64" t="n">
-        <v>6367558</v>
+        <v>6367556</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7924,7 +7915,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7934,7 +7925,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr">
@@ -7965,13 +7956,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658200</t>
+          <t>https://artportalen.se/Sighting/134658198</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134658202</v>
+        <v>134658199</v>
       </c>
       <c r="B65" t="n">
         <v>43472</v>
@@ -8006,13 +7997,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>716710</v>
+        <v>716721</v>
       </c>
       <c r="R65" t="n">
-        <v>6367554</v>
+        <v>6367546</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8041,7 +8032,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8051,12 +8042,12 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>5st</t>
+          <t>4st</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8082,13 +8073,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658202</t>
+          <t>https://artportalen.se/Sighting/134658199</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134658204</v>
+        <v>134658200</v>
       </c>
       <c r="B66" t="n">
         <v>43472</v>
@@ -8123,13 +8114,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>716692</v>
+        <v>716726</v>
       </c>
       <c r="R66" t="n">
-        <v>6367566</v>
+        <v>6367558</v>
       </c>
       <c r="S66" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8158,7 +8149,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8168,12 +8159,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>2st</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8199,16 +8190,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134658204</t>
+          <t>https://artportalen.se/Sighting/134658200</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133905926</v>
+        <v>134658202</v>
       </c>
       <c r="B67" t="n">
-        <v>58698</v>
+        <v>43472</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8216,56 +8207,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103055</v>
+        <v>101242</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>716777</v>
+        <v>716710</v>
       </c>
       <c r="R67" t="n">
-        <v>6367814</v>
+        <v>6367554</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8289,17 +8261,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Skog röjd på en och små lövträd.</t>
+          <t>5st</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8314,27 +8296,27 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133905926</t>
+          <t>https://artportalen.se/Sighting/134658202</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134134873</v>
+        <v>134658204</v>
       </c>
       <c r="B68" t="n">
-        <v>43469</v>
+        <v>43472</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8342,56 +8324,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>201116</v>
+        <v>101242</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Berggräsfjäril</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lasiommata petropolitana</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
+          <t>Ala, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>716824</v>
+        <v>716692</v>
       </c>
       <c r="R68" t="n">
-        <v>6367869</v>
+        <v>6367566</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8415,12 +8378,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8435,49 +8413,49 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134134873</t>
+          <t>https://artportalen.se/Sighting/134658204</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133906050</v>
+        <v>133905926</v>
       </c>
       <c r="B69" t="n">
-        <v>99173</v>
+        <v>58698</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>219798</v>
+        <v>103055</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -8485,29 +8463,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>716781</v>
+        <v>716777</v>
       </c>
       <c r="R69" t="n">
-        <v>6367774</v>
+        <v>6367814</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8539,6 +8522,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Skog röjd på en och små lövträd.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8547,11 +8535,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8567,38 +8550,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906050</t>
+          <t>https://artportalen.se/Sighting/133905926</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133906008</v>
+        <v>134134873</v>
       </c>
       <c r="B70" t="n">
-        <v>99224</v>
+        <v>43469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>219864</v>
+        <v>201116</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Berggräsfjäril</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Lasiommata petropolitana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -8608,19 +8591,29 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>716736</v>
+        <v>716824</v>
       </c>
       <c r="R70" t="n">
-        <v>6367574</v>
+        <v>6367869</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8664,11 +8657,6 @@
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
-      </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
@@ -8683,16 +8671,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906008</t>
+          <t>https://artportalen.se/Sighting/134134873</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133906069</v>
+        <v>133906050</v>
       </c>
       <c r="B71" t="n">
-        <v>99224</v>
+        <v>99173</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8700,37 +8688,51 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>219864</v>
+        <v>219798</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>716798</v>
+        <v>716781</v>
       </c>
       <c r="R71" t="n">
-        <v>6367869</v>
+        <v>6367774</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8762,11 +8764,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8778,7 +8775,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkhällmark, alvar.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8795,13 +8792,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906069</t>
+          <t>https://artportalen.se/Sighting/133906050</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133906072</v>
+        <v>133906008</v>
       </c>
       <c r="B72" t="n">
         <v>99224</v>
@@ -8831,7 +8828,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -8841,14 +8838,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>716824</v>
+        <v>716736</v>
       </c>
       <c r="R72" t="n">
-        <v>6367869</v>
+        <v>6367574</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8894,7 +8891,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8911,13 +8908,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906072</t>
+          <t>https://artportalen.se/Sighting/133906008</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133906077</v>
+        <v>133906069</v>
       </c>
       <c r="B73" t="n">
         <v>99224</v>
@@ -8945,29 +8942,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>716854</v>
+        <v>716798</v>
       </c>
       <c r="R73" t="n">
-        <v>6367916</v>
+        <v>6367869</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8999,6 +8987,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9010,7 +9003,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkhällmark, alvar.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9027,13 +9020,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906077</t>
+          <t>https://artportalen.se/Sighting/133906069</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133906105</v>
+        <v>133906072</v>
       </c>
       <c r="B74" t="n">
         <v>99224</v>
@@ -9063,7 +9056,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9073,14 +9066,14 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>716891</v>
+        <v>716824</v>
       </c>
       <c r="R74" t="n">
-        <v>6367995</v>
+        <v>6367869</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -9143,13 +9136,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906105</t>
+          <t>https://artportalen.se/Sighting/133906072</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133906108</v>
+        <v>133906077</v>
       </c>
       <c r="B75" t="n">
         <v>99224</v>
@@ -9193,10 +9186,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>716880</v>
+        <v>716854</v>
       </c>
       <c r="R75" t="n">
-        <v>6367998</v>
+        <v>6367916</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9259,16 +9252,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906108</t>
+          <t>https://artportalen.se/Sighting/133906077</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134649830</v>
+        <v>133906105</v>
       </c>
       <c r="B76" t="n">
-        <v>99230</v>
+        <v>99224</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9276,34 +9269,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219874</v>
+        <v>219864</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ala Ollajvs nedre, Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>716672</v>
+        <v>716891</v>
       </c>
       <c r="R76" t="n">
-        <v>6367566</v>
+        <v>6367995</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9330,22 +9332,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9356,69 +9348,83 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134649830</t>
+          <t>https://artportalen.se/Sighting/133906105</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133906065</v>
+        <v>133906108</v>
       </c>
       <c r="B77" t="n">
-        <v>104719</v>
+        <v>99224</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220164</v>
+        <v>219864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>716798</v>
+        <v>716880</v>
       </c>
       <c r="R77" t="n">
-        <v>6367869</v>
+        <v>6367998</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9461,7 +9467,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Kalkhällmark, alvar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9478,51 +9484,51 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906065</t>
+          <t>https://artportalen.se/Sighting/133906108</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133906001</v>
+        <v>134649830</v>
       </c>
       <c r="B78" t="n">
-        <v>110159</v>
+        <v>99230</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs nedre, Gtl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>716693</v>
+        <v>716672</v>
       </c>
       <c r="R78" t="n">
-        <v>6367557</v>
+        <v>6367566</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9549,12 +9555,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9565,36 +9581,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906001</t>
+          <t>https://artportalen.se/Sighting/134649830</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133906016</v>
+        <v>133906065</v>
       </c>
       <c r="B79" t="n">
-        <v>110159</v>
+        <v>104719</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9602,37 +9613,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220299</v>
+        <v>220164</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>716764</v>
+        <v>716798</v>
       </c>
       <c r="R79" t="n">
-        <v>6367627</v>
+        <v>6367869</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9675,7 +9686,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkhällmark, alvar.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -9692,13 +9703,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906016</t>
+          <t>https://artportalen.se/Sighting/133906065</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133906026</v>
+        <v>133906001</v>
       </c>
       <c r="B80" t="n">
         <v>110159</v>
@@ -9733,10 +9744,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>716755</v>
+        <v>716693</v>
       </c>
       <c r="R80" t="n">
-        <v>6367678</v>
+        <v>6367557</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9799,13 +9810,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906026</t>
+          <t>https://artportalen.se/Sighting/133906001</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133906028</v>
+        <v>133906016</v>
       </c>
       <c r="B81" t="n">
         <v>110159</v>
@@ -9840,10 +9851,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>716740</v>
+        <v>716764</v>
       </c>
       <c r="R81" t="n">
-        <v>6367688</v>
+        <v>6367627</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9906,13 +9917,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906028</t>
+          <t>https://artportalen.se/Sighting/133906016</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133906030</v>
+        <v>133906026</v>
       </c>
       <c r="B82" t="n">
         <v>110159</v>
@@ -9947,10 +9958,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>716719</v>
+        <v>716755</v>
       </c>
       <c r="R82" t="n">
-        <v>6367706</v>
+        <v>6367678</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -10013,13 +10024,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906030</t>
+          <t>https://artportalen.se/Sighting/133906026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133906034</v>
+        <v>133906028</v>
       </c>
       <c r="B83" t="n">
         <v>110159</v>
@@ -10054,10 +10065,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>716743</v>
+        <v>716740</v>
       </c>
       <c r="R83" t="n">
-        <v>6367714</v>
+        <v>6367688</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10120,13 +10131,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906034</t>
+          <t>https://artportalen.se/Sighting/133906028</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133906041</v>
+        <v>133906030</v>
       </c>
       <c r="B84" t="n">
         <v>110159</v>
@@ -10161,10 +10172,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>716731</v>
+        <v>716719</v>
       </c>
       <c r="R84" t="n">
-        <v>6367719</v>
+        <v>6367706</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10227,13 +10238,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906041</t>
+          <t>https://artportalen.se/Sighting/133906030</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133906043</v>
+        <v>133906034</v>
       </c>
       <c r="B85" t="n">
         <v>110159</v>
@@ -10268,10 +10279,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>716740</v>
+        <v>716743</v>
       </c>
       <c r="R85" t="n">
-        <v>6367726</v>
+        <v>6367714</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10334,13 +10345,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906043</t>
+          <t>https://artportalen.se/Sighting/133906034</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133906074</v>
+        <v>133906041</v>
       </c>
       <c r="B86" t="n">
         <v>110159</v>
@@ -10371,14 +10382,14 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>716847</v>
+        <v>716731</v>
       </c>
       <c r="R86" t="n">
-        <v>6367896</v>
+        <v>6367719</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -10413,11 +10424,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikt spridd.</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10429,7 +10435,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10446,13 +10452,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906074</t>
+          <t>https://artportalen.se/Sighting/133906041</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>133906078</v>
+        <v>133906043</v>
       </c>
       <c r="B87" t="n">
         <v>110159</v>
@@ -10483,14 +10489,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>716854</v>
+        <v>716740</v>
       </c>
       <c r="R87" t="n">
-        <v>6367916</v>
+        <v>6367726</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -10525,11 +10531,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10541,7 +10542,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, delvis sumpskog.</t>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10558,13 +10559,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906078</t>
+          <t>https://artportalen.se/Sighting/133906043</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133906080</v>
+        <v>133906074</v>
       </c>
       <c r="B88" t="n">
         <v>110159</v>
@@ -10602,7 +10603,7 @@
         <v>716847</v>
       </c>
       <c r="R88" t="n">
-        <v>6367921</v>
+        <v>6367896</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10637,6 +10638,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Rikt spridd.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10665,13 +10671,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906080</t>
+          <t>https://artportalen.se/Sighting/133906074</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133906082</v>
+        <v>133906078</v>
       </c>
       <c r="B89" t="n">
         <v>110159</v>
@@ -10706,10 +10712,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>716824</v>
+        <v>716854</v>
       </c>
       <c r="R89" t="n">
-        <v>6367939</v>
+        <v>6367916</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10746,7 +10752,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Rikt spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10777,13 +10783,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906082</t>
+          <t>https://artportalen.se/Sighting/133906078</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133906090</v>
+        <v>133906080</v>
       </c>
       <c r="B90" t="n">
         <v>110159</v>
@@ -10818,10 +10824,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>716837</v>
+        <v>716847</v>
       </c>
       <c r="R90" t="n">
-        <v>6367949</v>
+        <v>6367921</v>
       </c>
       <c r="S90" t="n">
         <v>5</v>
@@ -10884,13 +10890,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906090</t>
+          <t>https://artportalen.se/Sighting/133906080</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133906092</v>
+        <v>133906082</v>
       </c>
       <c r="B91" t="n">
         <v>110159</v>
@@ -10925,10 +10931,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>716848</v>
+        <v>716824</v>
       </c>
       <c r="R91" t="n">
-        <v>6367955</v>
+        <v>6367939</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10965,7 +10971,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Rikt spridd.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10996,13 +11002,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906092</t>
+          <t>https://artportalen.se/Sighting/133906082</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133906094</v>
+        <v>133906090</v>
       </c>
       <c r="B92" t="n">
         <v>110159</v>
@@ -11037,10 +11043,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>716858</v>
+        <v>716837</v>
       </c>
       <c r="R92" t="n">
-        <v>6367961</v>
+        <v>6367949</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -11075,11 +11081,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -11108,13 +11109,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906094</t>
+          <t>https://artportalen.se/Sighting/133906090</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133906096</v>
+        <v>133906092</v>
       </c>
       <c r="B93" t="n">
         <v>110159</v>
@@ -11149,10 +11150,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>716857</v>
+        <v>716848</v>
       </c>
       <c r="R93" t="n">
-        <v>6367975</v>
+        <v>6367955</v>
       </c>
       <c r="S93" t="n">
         <v>5</v>
@@ -11189,7 +11190,7 @@
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Rikligt spridd.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11220,13 +11221,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906096</t>
+          <t>https://artportalen.se/Sighting/133906092</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133906100</v>
+        <v>133906094</v>
       </c>
       <c r="B94" t="n">
         <v>110159</v>
@@ -11261,10 +11262,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>716857</v>
+        <v>716858</v>
       </c>
       <c r="R94" t="n">
-        <v>6367987</v>
+        <v>6367961</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11299,6 +11300,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD94" t="b">
         <v>0</v>
       </c>
@@ -11327,13 +11333,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906100</t>
+          <t>https://artportalen.se/Sighting/133906094</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133906102</v>
+        <v>133906096</v>
       </c>
       <c r="B95" t="n">
         <v>110159</v>
@@ -11368,10 +11374,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>716870</v>
+        <v>716857</v>
       </c>
       <c r="R95" t="n">
-        <v>6367996</v>
+        <v>6367975</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11439,13 +11445,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906102</t>
+          <t>https://artportalen.se/Sighting/133906096</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133906106</v>
+        <v>133906100</v>
       </c>
       <c r="B96" t="n">
         <v>110159</v>
@@ -11480,10 +11486,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>716891</v>
+        <v>716857</v>
       </c>
       <c r="R96" t="n">
-        <v>6367995</v>
+        <v>6367987</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -11518,11 +11524,6 @@
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt spridd.</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11551,13 +11552,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906106</t>
+          <t>https://artportalen.se/Sighting/133906100</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133906109</v>
+        <v>133906102</v>
       </c>
       <c r="B97" t="n">
         <v>110159</v>
@@ -11592,10 +11593,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>716880</v>
+        <v>716870</v>
       </c>
       <c r="R97" t="n">
-        <v>6367998</v>
+        <v>6367996</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11663,13 +11664,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906109</t>
+          <t>https://artportalen.se/Sighting/133906102</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133906111</v>
+        <v>133906106</v>
       </c>
       <c r="B98" t="n">
         <v>110159</v>
@@ -11704,10 +11705,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>716880</v>
+        <v>716891</v>
       </c>
       <c r="R98" t="n">
-        <v>6367991</v>
+        <v>6367995</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11775,13 +11776,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906111</t>
+          <t>https://artportalen.se/Sighting/133906106</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133906113</v>
+        <v>133906109</v>
       </c>
       <c r="B99" t="n">
         <v>110159</v>
@@ -11816,10 +11817,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>716867</v>
+        <v>716880</v>
       </c>
       <c r="R99" t="n">
-        <v>6367982</v>
+        <v>6367998</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11887,13 +11888,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906113</t>
+          <t>https://artportalen.se/Sighting/133906109</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133906116</v>
+        <v>133906111</v>
       </c>
       <c r="B100" t="n">
         <v>110159</v>
@@ -11928,13 +11929,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>716870</v>
+        <v>716880</v>
       </c>
       <c r="R100" t="n">
-        <v>6367944</v>
+        <v>6367991</v>
       </c>
       <c r="S100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11968,7 +11969,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
+          <t>Rikligt spridd.</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11999,16 +12000,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906116</t>
+          <t>https://artportalen.se/Sighting/133906111</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133906064</v>
+        <v>133906113</v>
       </c>
       <c r="B101" t="n">
-        <v>107598</v>
+        <v>110159</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12016,16 +12017,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -12036,17 +12037,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>716798</v>
+        <v>716867</v>
       </c>
       <c r="R101" t="n">
-        <v>6367869</v>
+        <v>6367982</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12078,6 +12079,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt spridd.</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12089,7 +12095,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Kalkhällmark, alvar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -12106,33 +12112,33 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906064</t>
+          <t>https://artportalen.se/Sighting/133906113</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133906012</v>
+        <v>133906116</v>
       </c>
       <c r="B102" t="n">
-        <v>99001</v>
+        <v>110159</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>223049</v>
+        <v>220299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -12143,17 +12149,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+          <t>Ala Ollajvs 1:26 körväg N, A 63149-2025., Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>716740</v>
+        <v>716870</v>
       </c>
       <c r="R102" t="n">
-        <v>6367716</v>
+        <v>6367944</v>
       </c>
       <c r="S102" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12185,6 +12191,11 @@
           <t>2026-05-20</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Skogen buskröjd inför avverkning. Mellanskog.</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
@@ -12196,7 +12207,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, röjd på småbuskar.</t>
+          <t>Kalkbarrskog, delvis sumpskog.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12213,54 +12224,54 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133906012</t>
+          <t>https://artportalen.se/Sighting/133906116</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134649829</v>
+        <v>133906064</v>
       </c>
       <c r="B103" t="n">
-        <v>99113</v>
+        <v>107598</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>223591</v>
+        <v>221849</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ala Ollajvs nedre, Gtl</t>
+          <t>Ala Ollajvs 1:26, körväg N., Gtl</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>716672</v>
+        <v>716798</v>
       </c>
       <c r="R103" t="n">
-        <v>6367566</v>
+        <v>6367869</v>
       </c>
       <c r="S103" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12284,22 +12295,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>11:15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12310,22 +12311,472 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>Kalkhällmark, alvar.</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anna Helmersson</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/133906064</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>133906012</v>
+      </c>
+      <c r="B104" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs 1:26, körväg S. A 63149-2025., Gtl</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>716740</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6367716</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, röjd på småbuskar.</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133906012</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>134649829</v>
+      </c>
+      <c r="B105" t="n">
+        <v>99113</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ala Ollajvs nedre, Gtl</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>716672</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6367566</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anna Helmersson</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134649829</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>137406589</v>
+      </c>
+      <c r="B106" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ala, Gtl</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>716695</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6367773</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137406589</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>137406592</v>
+      </c>
+      <c r="B107" t="n">
+        <v>87578</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ala, Gtl</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>716715</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6367566</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF107" t="inlineStr"/>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137406592</t>
         </is>
       </c>
     </row>
@@ -12433,6 +12884,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406599</v>
       </c>
       <c r="B2" t="n">
-        <v>101655</v>
+        <v>101667</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>137406590</v>
       </c>
       <c r="B4" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>137406589</v>
       </c>
       <c r="B106" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>137406592</v>
       </c>
       <c r="B107" t="n">
-        <v>87578</v>
+        <v>87589</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406599</v>
       </c>
       <c r="B2" t="n">
-        <v>101667</v>
+        <v>101668</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>137406590</v>
       </c>
       <c r="B4" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>137406589</v>
       </c>
       <c r="B106" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>137406592</v>
       </c>
       <c r="B107" t="n">
-        <v>87589</v>
+        <v>87590</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406599</v>
       </c>
       <c r="B2" t="n">
-        <v>101668</v>
+        <v>101671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>137406590</v>
       </c>
       <c r="B4" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>137406589</v>
       </c>
       <c r="B106" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>137406592</v>
       </c>
       <c r="B107" t="n">
-        <v>87590</v>
+        <v>87593</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 63149-2025 artfynd.xlsx
+++ b/artfynd/A 63149-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137406599</v>
       </c>
       <c r="B2" t="n">
-        <v>101671</v>
+        <v>101675</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>137406590</v>
       </c>
       <c r="B4" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -12559,7 +12559,7 @@
         <v>137406589</v>
       </c>
       <c r="B106" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>137406592</v>
       </c>
       <c r="B107" t="n">
-        <v>87593</v>
+        <v>87597</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
